--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487125_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487125_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6891</v>
+        <v>2.6623</v>
       </c>
       <c r="E2" t="n">
         <v>1.9034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7857</v>
+        <v>0.7589</v>
       </c>
       <c r="G2" t="n">
         <v>1.36</v>
@@ -610,13 +610,13 @@
         <v>0.386</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2849</v>
+        <v>-0.3117</v>
       </c>
       <c r="T2" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0126</v>
+        <v>-0.0142</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2002</v>
+        <v>1.646</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0839</v>
+        <v>4.5832</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8837</v>
+        <v>-2.9373</v>
       </c>
       <c r="G3" t="n">
         <v>0.153</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4667</v>
+        <v>-1.0209</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.152</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3147</v>
+        <v>-0.3682</v>
       </c>
       <c r="V3" t="n">
         <v>2.1278</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8045</v>
+        <v>-0.5982</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1339</v>
+        <v>0.3668</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6706</v>
+        <v>-0.965</v>
       </c>
       <c r="G5" t="n">
         <v>0.8506</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2341</v>
+        <v>-1.0278</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1898</v>
+        <v>-0.6891</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0443</v>
+        <v>-0.3388</v>
       </c>
       <c r="V5" t="n">
         <v>-0.614</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3788</v>
+        <v>-1.3917</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2289</v>
+        <v>-0.4292</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1499</v>
+        <v>-0.9625</v>
       </c>
       <c r="G6" t="n">
         <v>1.1911</v>
@@ -922,13 +922,13 @@
         <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0331</v>
+        <v>-1.046</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2842</v>
+        <v>-0.4845</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7489</v>
+        <v>-0.5615</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5717</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6393</v>
+        <v>-2.7705</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07290000000000001</v>
+        <v>-1.4298</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7123</v>
+        <v>-1.3407</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0508</v>
+        <v>-1.9761</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4668</v>
+        <v>-1.9469</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.584</v>
+        <v>-0.0293</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8881</v>
+        <v>-0.6012</v>
       </c>
       <c r="K8" t="n">
-        <v>1.009</v>
+        <v>-1.2524</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8971</v>
+        <v>0.6512</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1627</v>
+        <v>-1.3749</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4758</v>
+        <v>-0.6944</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6869</v>
+        <v>-0.6805</v>
       </c>
       <c r="P8" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.31</v>
+        <v>-0.5242</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2247</v>
+        <v>-0.4352</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0853</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2436</v>
+        <v>-0.6562</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1857</v>
+        <v>0.5717</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4293</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8974</v>
+        <v>-2.913</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5299</v>
+        <v>-0.2275</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3675</v>
+        <v>-2.6855</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9761</v>
+        <v>-3.0508</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9469</v>
+        <v>-0.4668</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0293</v>
+        <v>-2.584</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6012</v>
+        <v>-0.8881</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2524</v>
+        <v>1.009</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6512</v>
+        <v>-1.8971</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3749</v>
+        <v>-2.1627</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6944</v>
+        <v>-1.4758</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6869</v>
       </c>
       <c r="P9" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6511</v>
+        <v>-0.5836</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5354</v>
+        <v>-0.5251</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1157</v>
+        <v>-0.0585</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6562</v>
+        <v>-0.2436</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5717</v>
+        <v>1.1857</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>-1.4293</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8898</v>
+        <v>-3.6896</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3115</v>
+        <v>-1.1112</v>
       </c>
       <c r="F10" t="n">
         <v>-2.5783</v>
@@ -1234,10 +1234,10 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.084</v>
+        <v>-0.8837</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>-0.2161</v>
       </c>
       <c r="U10" t="n">
         <v>-0.6676</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4056</v>
+        <v>-4.7933</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.481</v>
+        <v>-4.6813</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07539999999999999</v>
+        <v>-0.112</v>
       </c>
       <c r="G11" t="n">
         <v>-1.307</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3616</v>
+        <v>-0.7492</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5221</v>
+        <v>-0.7224</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1606</v>
+        <v>-0.0268</v>
       </c>
       <c r="V11" t="n">
         <v>-0.614</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.8319</v>
+        <v>-11.1101</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7813</v>
+        <v>-9.380800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0506</v>
+        <v>-1.7293</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7423999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7854</v>
+        <v>-2.0636</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4277</v>
+        <v>-1.0271</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3577</v>
+        <v>-1.0365</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1278</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.4935</v>
+        <v>-25.4936</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.5622</v>
+        <v>-12.5623</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.9315</v>
+        <v>-12.9314</v>
       </c>
       <c r="G13" t="n">
         <v>-5.2447</v>
@@ -1468,10 +1468,10 @@
         <v>14.4755</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.2804</v>
+        <v>-9.280200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.882499999999999</v>
+        <v>-5.882400000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-3.3976</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2992</v>
+        <v>6.6598</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9031</v>
+        <v>4.1708</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3961</v>
+        <v>2.489</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>2.2162</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5265</v>
+        <v>3.5086</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2835</v>
+        <v>-1.2924</v>
       </c>
       <c r="J14" t="n">
-        <v>2.424</v>
+        <v>2.2082</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2612</v>
+        <v>2.7944</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1628</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6141</v>
+        <v>0.008</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7347</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1207</v>
+        <v>-0.7062</v>
       </c>
       <c r="P14" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R14" t="n">
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9248</v>
+        <v>0.6716</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0378</v>
+        <v>0.3137</v>
       </c>
       <c r="U14" t="n">
-        <v>0.887</v>
+        <v>0.3579</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3714</v>
+        <v>1.842</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3714</v>
+        <v>1.842</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2551</v>
+        <v>6.6146</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6844</v>
+        <v>4.8802</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5706</v>
+        <v>1.7343</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3901</v>
+        <v>3.9922</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0987</v>
+        <v>0.707</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2913</v>
+        <v>3.2852</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8636</v>
+        <v>5.1397</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2859</v>
+        <v>1.4282</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5777</v>
+        <v>3.7115</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4735</v>
+        <v>-1.1476</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1872</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2863</v>
+        <v>-0.4263</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-1.158</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1231</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5671</v>
+        <v>0.8504</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1322</v>
+        <v>0.2846</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4349</v>
+        <v>0.5658</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0699</v>
+        <v>0.614</v>
       </c>
       <c r="W15" t="n">
-        <v>4.5838</v>
+        <v>0.614</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9043</v>
+        <v>6.3155</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8704</v>
+        <v>5.5843</v>
       </c>
       <c r="F16" t="n">
-        <v>2.034</v>
+        <v>0.7312</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2162</v>
+        <v>3.3901</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5086</v>
+        <v>3.0987</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2924</v>
+        <v>0.2913</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2082</v>
+        <v>3.8636</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7944</v>
+        <v>3.2859</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.5777</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008</v>
+        <v>-0.4735</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7141999999999999</v>
+        <v>-0.1872</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7062</v>
+        <v>-0.2863</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9301</v>
+        <v>-0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.193</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0839</v>
+        <v>0.6276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0132</v>
+        <v>0.0321</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.5955</v>
       </c>
       <c r="V16" t="n">
-        <v>1.842</v>
+        <v>3.0699</v>
       </c>
       <c r="W16" t="n">
-        <v>1.842</v>
+        <v>4.5838</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5923</v>
+        <v>5.745</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1793</v>
+        <v>3.4024</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4131</v>
+        <v>2.3425</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9922</v>
+        <v>1.81</v>
       </c>
       <c r="H17" t="n">
-        <v>0.707</v>
+        <v>1.5265</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2852</v>
+        <v>0.2835</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1397</v>
+        <v>2.424</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4282</v>
+        <v>2.2612</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7115</v>
+        <v>0.1628</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1476</v>
+        <v>-0.6141</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7347</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4263</v>
+        <v>0.1207</v>
       </c>
       <c r="P17" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1719</v>
+        <v>1.3705</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4164</v>
+        <v>0.5371</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2446</v>
+        <v>0.8335</v>
       </c>
       <c r="V17" t="n">
-        <v>0.614</v>
+        <v>2.3714</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>2.3714</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4724</v>
+        <v>3.3674</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0254</v>
+        <v>1.3253</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4977</v>
+        <v>2.0421</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2691</v>
+        <v>0.7664</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6915</v>
+        <v>-0.0362</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5777</v>
+        <v>0.8026</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0632</v>
+        <v>0.7997</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1853</v>
+        <v>0.1242</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1221</v>
+        <v>0.6755</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2059</v>
+        <v>-0.0333</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4938</v>
+        <v>-0.1604</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6998</v>
+        <v>0.1271</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7021</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6672</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9236</v>
+        <v>0.7096</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6591</v>
+        <v>0.2628</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2645</v>
+        <v>0.4468</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8842</v>
+        <v>1.3125</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9738</v>
+        <v>1.2604</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8246</v>
+        <v>-2.3272</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1492</v>
+        <v>3.5876</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7664</v>
+        <v>-1.2691</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0362</v>
+        <v>-0.6915</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8026</v>
+        <v>-0.5777</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7997</v>
+        <v>-1.0632</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1242</v>
+        <v>-1.1853</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6755</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0333</v>
+        <v>-0.2059</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1604</v>
+        <v>0.4938</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1271</v>
+        <v>-0.6998</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>2.7021</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>3.6672</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3159</v>
+        <v>1.7116</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.238</v>
+        <v>0.3573</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5538999999999999</v>
+        <v>1.3543</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3125</v>
+        <v>-1.8842</v>
       </c>
       <c r="W19" t="n">
-        <v>1.228</v>
+        <v>-0.6562</v>
       </c>
       <c r="X19" t="n">
-        <v>0.08450000000000001</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9782999999999999</v>
+        <v>-0.2838</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6999</v>
+        <v>1.5983</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7215</v>
+        <v>-1.8821</v>
       </c>
       <c r="G20" t="n">
         <v>0.5822000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2381</v>
+        <v>0.976</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8838</v>
+        <v>0.7823</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3543</v>
+        <v>0.1937</v>
       </c>
       <c r="V20" t="n">
         <v>-1.842</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8676</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7297</v>
+        <v>-1.4293</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8621</v>
+        <v>0.9157</v>
       </c>
       <c r="G21" t="n">
         <v>0.3565</v>
@@ -2092,13 +2092,13 @@
         <v>2.3161</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3622</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1652</v>
+        <v>0.1352</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5274</v>
+        <v>0.581</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0422</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5028</v>
+        <v>-0.7635</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6282</v>
+        <v>0.2077</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1255</v>
+        <v>-0.9712</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1441</v>
+        <v>-1.7098</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4768</v>
+        <v>-0.6387</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6672</v>
+        <v>-1.071</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.8781</v>
+        <v>-0.1686</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.51</v>
+        <v>0.3362</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.368</v>
+        <v>-0.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.266</v>
+        <v>-1.5411</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0332</v>
+        <v>-0.9749</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2992</v>
+        <v>-0.5662</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3161</v>
+        <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5182</v>
+        <v>0.7532</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4429</v>
+        <v>0.3064</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.4468</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5577</v>
+        <v>-1.4353</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6936</v>
+        <v>-3.8285</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8642</v>
+        <v>2.3931</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7098</v>
+        <v>-4.1441</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6387</v>
+        <v>-2.4768</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.071</v>
+        <v>-1.6672</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1686</v>
+        <v>-3.8781</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3362</v>
+        <v>-2.51</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5048</v>
+        <v>-1.368</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5411</v>
+        <v>-0.266</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9749</v>
+        <v>0.0332</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5662</v>
+        <v>-0.2992</v>
       </c>
       <c r="P23" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.041</v>
+        <v>0.5856</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5949</v>
+        <v>0.2426</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.343</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0538</v>
+        <v>-1.4728</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1535</v>
+        <v>-0.6528</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9003</v>
+        <v>-0.82</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7458</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.273</v>
+        <v>0.308</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3569</v>
+        <v>0.1438</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0839</v>
+        <v>0.1642</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>25.4935</v>
+        <v>25.4937</v>
       </c>
       <c r="E25" t="n">
-        <v>12.9313</v>
+        <v>12.9312</v>
       </c>
       <c r="F25" t="n">
-        <v>12.5623</v>
+        <v>12.5622</v>
       </c>
       <c r="G25" t="n">
         <v>5.244800000000001</v>
@@ -2404,10 +2404,10 @@
         <v>21.231</v>
       </c>
       <c r="S25" t="n">
-        <v>9.280100000000001</v>
+        <v>9.280299999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>3.3976</v>
+        <v>3.3979</v>
       </c>
       <c r="U25" t="n">
         <v>5.882499999999999</v>
